--- a/output/generated_boq.xlsx
+++ b/output/generated_boq.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Room_1</t>
+          <t>Room 1</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>33.53</v>
+        <v>12.64</v>
       </c>
       <c r="G2" t="n">
         <v>5200</v>
       </c>
       <c r="H2" t="n">
-        <v>174376.8</v>
+        <v>65732.16</v>
       </c>
     </row>
     <row r="3">
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Room_1</t>
+          <t>Room 1</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>145.8</v>
+        <v>54.96</v>
       </c>
       <c r="G3" t="n">
         <v>220</v>
       </c>
       <c r="H3" t="n">
-        <v>32076</v>
+        <v>12091.2</v>
       </c>
     </row>
     <row r="4">
@@ -540,7 +540,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Room_1</t>
+          <t>Room 1</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>146.93</v>
+        <v>20.69</v>
       </c>
       <c r="G4" t="n">
         <v>950</v>
       </c>
       <c r="H4" t="n">
-        <v>139583.5</v>
+        <v>19655.5</v>
       </c>
     </row>
     <row r="5">
@@ -572,7 +572,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Room_1</t>
+          <t>Room 1</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -589,13 +589,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>145.8</v>
+        <v>54.96</v>
       </c>
       <c r="G5" t="n">
         <v>120</v>
       </c>
       <c r="H5" t="n">
-        <v>17496</v>
+        <v>6595.2</v>
       </c>
     </row>
     <row r="6">
@@ -604,7 +604,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Room_2</t>
+          <t>Room 2</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>35.08</v>
+        <v>12.08</v>
       </c>
       <c r="G6" t="n">
         <v>5200</v>
       </c>
       <c r="H6" t="n">
-        <v>182413.92</v>
+        <v>62790</v>
       </c>
     </row>
     <row r="7">
@@ -636,7 +636,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Room_2</t>
+          <t>Room 2</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>152.52</v>
+        <v>52.5</v>
       </c>
       <c r="G7" t="n">
         <v>220</v>
       </c>
       <c r="H7" t="n">
-        <v>33554.4</v>
+        <v>11550</v>
       </c>
     </row>
     <row r="8">
@@ -668,7 +668,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Room_2</t>
+          <t>Room 2</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>159.61</v>
+        <v>19.04</v>
       </c>
       <c r="G8" t="n">
         <v>950</v>
       </c>
       <c r="H8" t="n">
-        <v>151629.5</v>
+        <v>18088</v>
       </c>
     </row>
     <row r="9">
@@ -700,7 +700,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Room_2</t>
+          <t>Room 2</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>152.52</v>
+        <v>52.5</v>
       </c>
       <c r="G9" t="n">
         <v>120</v>
       </c>
       <c r="H9" t="n">
-        <v>18302.4</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="10">
@@ -739,7 +739,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>749432.52</v>
+        <v>202802.06</v>
       </c>
     </row>
   </sheetData>
